--- a/artfynd/A 58525-2023 artfynd.xlsx
+++ b/artfynd/A 58525-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493424</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,14 +781,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>126493423</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,14 +895,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>126493420</v>
       </c>
       <c r="B4" t="n">
-        <v>79598</v>
+        <v>79739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -988,14 +996,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>126493430</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,7 +1097,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58525-2023 artfynd.xlsx
+++ b/artfynd/A 58525-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493424</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>126493423</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>126493420</v>
       </c>
       <c r="B4" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>126493430</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58525-2023 artfynd.xlsx
+++ b/artfynd/A 58525-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493424</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>126493423</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>126493420</v>
       </c>
       <c r="B4" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>126493430</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58525-2023 artfynd.xlsx
+++ b/artfynd/A 58525-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>126493420</v>
       </c>
       <c r="B4" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>126493430</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58525-2023 artfynd.xlsx
+++ b/artfynd/A 58525-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493424</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>126493423</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>126493420</v>
       </c>
       <c r="B4" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>126493430</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58525-2023 artfynd.xlsx
+++ b/artfynd/A 58525-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126493424</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>126493423</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>126493420</v>
       </c>
       <c r="B4" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>126493430</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58525-2023 artfynd.xlsx
+++ b/artfynd/A 58525-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>126493420</v>
       </c>
       <c r="B4" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>126493430</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58525-2023 artfynd.xlsx
+++ b/artfynd/A 58525-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>126493420</v>
       </c>
       <c r="B4" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>126493430</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
